--- a/artfynd/A 47248-2025 artfynd.xlsx
+++ b/artfynd/A 47248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>98403257</v>
       </c>
       <c r="B2" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47248-2025 artfynd.xlsx
+++ b/artfynd/A 47248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>98403257</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47248-2025 artfynd.xlsx
+++ b/artfynd/A 47248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>98403257</v>
       </c>
       <c r="B2" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47248-2025 artfynd.xlsx
+++ b/artfynd/A 47248-2025 artfynd.xlsx
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hovid 133, Sundsvall, Mpd</t>

--- a/artfynd/A 47248-2025 artfynd.xlsx
+++ b/artfynd/A 47248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>98403257</v>
       </c>
       <c r="B2" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47248-2025 artfynd.xlsx
+++ b/artfynd/A 47248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>98403257</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47248-2025 artfynd.xlsx
+++ b/artfynd/A 47248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>98403257</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47248-2025 artfynd.xlsx
+++ b/artfynd/A 47248-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>98403257</v>
       </c>
       <c r="B2" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
